--- a/database/event/5464/event_5464_evp_summary.xlsx
+++ b/database/event/5464/event_5464_evp_summary.xlsx
@@ -496,25 +496,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9.6281</v>
+        <v>9.6052</v>
       </c>
       <c r="C2" t="n">
-        <v>1.9204</v>
+        <v>1.9158</v>
       </c>
       <c r="D2" t="n">
-        <v>3.4682</v>
+        <v>3.3828</v>
       </c>
       <c r="E2" t="n">
-        <v>9.6281</v>
+        <v>9.6052</v>
       </c>
       <c r="F2" t="n">
-        <v>4.5499</v>
+        <v>4.527</v>
       </c>
       <c r="G2" t="n">
         <v>5.0782</v>
       </c>
       <c r="H2" t="n">
-        <v>4.8313</v>
+        <v>4.7953</v>
       </c>
       <c r="I2" t="n">
         <v>4.8763</v>
@@ -542,25 +542,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.8132</v>
+        <v>7.7214</v>
       </c>
       <c r="C3" t="n">
-        <v>1.5584</v>
+        <v>1.5401</v>
       </c>
       <c r="D3" t="n">
-        <v>2.735</v>
+        <v>2.6323</v>
       </c>
       <c r="E3" t="n">
-        <v>7.8132</v>
+        <v>7.7214</v>
       </c>
       <c r="F3" t="n">
-        <v>6.4283</v>
+        <v>6.3365</v>
       </c>
       <c r="G3" t="n">
         <v>1.3849</v>
       </c>
       <c r="H3" t="n">
-        <v>7.7765</v>
+        <v>7.6325</v>
       </c>
       <c r="I3" t="n">
         <v>7.9592</v>
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.8341</v>
+        <v>6.7475</v>
       </c>
       <c r="C4" t="n">
-        <v>1.3631</v>
+        <v>1.3459</v>
       </c>
       <c r="D4" t="n">
-        <v>2.3395</v>
+        <v>2.2443</v>
       </c>
       <c r="E4" t="n">
-        <v>6.8341</v>
+        <v>6.7475</v>
       </c>
       <c r="F4" t="n">
-        <v>6.1468</v>
+        <v>6.0602</v>
       </c>
       <c r="G4" t="n">
         <v>0.6873</v>
       </c>
       <c r="H4" t="n">
-        <v>7.3351</v>
+        <v>7.1993</v>
       </c>
       <c r="I4" t="n">
         <v>7.5074</v>
@@ -634,25 +634,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.6468</v>
+        <v>6.6174</v>
       </c>
       <c r="C5" t="n">
-        <v>1.3258</v>
+        <v>1.3199</v>
       </c>
       <c r="D5" t="n">
-        <v>2.2638</v>
+        <v>2.1925</v>
       </c>
       <c r="E5" t="n">
-        <v>6.6468</v>
+        <v>6.6174</v>
       </c>
       <c r="F5" t="n">
-        <v>3.9466</v>
+        <v>3.9172</v>
       </c>
       <c r="G5" t="n">
         <v>2.7002</v>
       </c>
       <c r="H5" t="n">
-        <v>3.9466</v>
+        <v>3.9172</v>
       </c>
       <c r="I5" t="n">
         <v>3.9834</v>
@@ -680,25 +680,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.3844</v>
+        <v>6.3657</v>
       </c>
       <c r="C6" t="n">
-        <v>1.2734</v>
+        <v>1.2697</v>
       </c>
       <c r="D6" t="n">
-        <v>2.1578</v>
+        <v>2.0922</v>
       </c>
       <c r="E6" t="n">
-        <v>6.3844</v>
+        <v>6.3657</v>
       </c>
       <c r="F6" t="n">
-        <v>2.5136</v>
+        <v>2.4949</v>
       </c>
       <c r="G6" t="n">
         <v>3.8708</v>
       </c>
       <c r="H6" t="n">
-        <v>2.5136</v>
+        <v>2.4949</v>
       </c>
       <c r="I6" t="n">
         <v>2.5371</v>
@@ -732,7 +732,7 @@
         <v>1.1871</v>
       </c>
       <c r="D7" t="n">
-        <v>1.983</v>
+        <v>1.9272</v>
       </c>
       <c r="E7" t="n">
         <v>5.9517</v>
@@ -772,25 +772,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.7669</v>
+        <v>5.7456</v>
       </c>
       <c r="C8" t="n">
-        <v>1.1503</v>
+        <v>1.146</v>
       </c>
       <c r="D8" t="n">
-        <v>1.9083</v>
+        <v>1.8451</v>
       </c>
       <c r="E8" t="n">
-        <v>5.7669</v>
+        <v>5.7456</v>
       </c>
       <c r="F8" t="n">
-        <v>4.3201</v>
+        <v>4.2988</v>
       </c>
       <c r="G8" t="n">
         <v>1.4468</v>
       </c>
       <c r="H8" t="n">
-        <v>4.4708</v>
+        <v>4.4375</v>
       </c>
       <c r="I8" t="n">
         <v>4.5125</v>
@@ -824,7 +824,7 @@
         <v>1.1346</v>
       </c>
       <c r="D9" t="n">
-        <v>1.8765</v>
+        <v>1.8223</v>
       </c>
       <c r="E9" t="n">
         <v>5.6882</v>
@@ -870,7 +870,7 @@
         <v>1.0647</v>
       </c>
       <c r="D10" t="n">
-        <v>1.7351</v>
+        <v>1.6828</v>
       </c>
       <c r="E10" t="n">
         <v>5.3381</v>
@@ -906,93 +906,93 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Xeppaa</t>
+          <t>b4rtiN</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5.169</v>
+        <v>5.1647</v>
       </c>
       <c r="C11" t="n">
-        <v>1.031</v>
+        <v>1.0301</v>
       </c>
       <c r="D11" t="n">
-        <v>1.6668</v>
+        <v>1.6137</v>
       </c>
       <c r="E11" t="n">
-        <v>5.169</v>
+        <v>5.1647</v>
       </c>
       <c r="F11" t="n">
-        <v>5.169</v>
+        <v>4.7932</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>0.3715</v>
       </c>
       <c r="H11" t="n">
-        <v>5.8019</v>
+        <v>5.2127</v>
       </c>
       <c r="I11" t="n">
-        <v>5.8289</v>
+        <v>5.2127</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>0.3715</v>
       </c>
       <c r="K11" t="n">
-        <v>284</v>
+        <v>388</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="M11" t="n">
-        <v>5.8289</v>
+        <v>5.5842</v>
       </c>
       <c r="N11" t="n">
-        <v>284</v>
+        <v>516</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>b4rtiN</t>
+          <t>Xeppaa</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>5.1647</v>
+        <v>5.1552</v>
       </c>
       <c r="C12" t="n">
-        <v>1.0301</v>
+        <v>1.0283</v>
       </c>
       <c r="D12" t="n">
-        <v>1.6651</v>
+        <v>1.6099</v>
       </c>
       <c r="E12" t="n">
-        <v>5.1647</v>
+        <v>5.1552</v>
       </c>
       <c r="F12" t="n">
-        <v>4.7932</v>
+        <v>5.1552</v>
       </c>
       <c r="G12" t="n">
-        <v>0.3715</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>5.2127</v>
+        <v>5.7802</v>
       </c>
       <c r="I12" t="n">
-        <v>5.2127</v>
+        <v>5.8289</v>
       </c>
       <c r="J12" t="n">
-        <v>0.3715</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>388</v>
+        <v>284</v>
       </c>
       <c r="L12" t="n">
-        <v>128</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>5.5842</v>
+        <v>5.8289</v>
       </c>
       <c r="N12" t="n">
-        <v>516</v>
+        <v>284</v>
       </c>
     </row>
     <row r="13">
@@ -1002,25 +1002,25 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>5.1047</v>
+        <v>5.0506</v>
       </c>
       <c r="C13" t="n">
-        <v>1.0182</v>
+        <v>1.0074</v>
       </c>
       <c r="D13" t="n">
-        <v>1.6408</v>
+        <v>1.5682</v>
       </c>
       <c r="E13" t="n">
-        <v>5.1047</v>
+        <v>5.0506</v>
       </c>
       <c r="F13" t="n">
-        <v>4.3905</v>
+        <v>4.3364</v>
       </c>
       <c r="G13" t="n">
         <v>0.7141999999999999</v>
       </c>
       <c r="H13" t="n">
-        <v>4.5812</v>
+        <v>4.4964</v>
       </c>
       <c r="I13" t="n">
         <v>4.6888</v>
@@ -1054,7 +1054,7 @@
         <v>0.9555</v>
       </c>
       <c r="D14" t="n">
-        <v>1.5138</v>
+        <v>1.4645</v>
       </c>
       <c r="E14" t="n">
         <v>4.7903</v>
@@ -1100,7 +1100,7 @@
         <v>0.95</v>
       </c>
       <c r="D15" t="n">
-        <v>1.5028</v>
+        <v>1.4537</v>
       </c>
       <c r="E15" t="n">
         <v>4.7631</v>
@@ -1146,7 +1146,7 @@
         <v>0.899</v>
       </c>
       <c r="D16" t="n">
-        <v>1.3995</v>
+        <v>1.3518</v>
       </c>
       <c r="E16" t="n">
         <v>4.5073</v>
@@ -1186,25 +1186,25 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4.3032</v>
+        <v>4.2769</v>
       </c>
       <c r="C17" t="n">
-        <v>0.8583</v>
+        <v>0.8531</v>
       </c>
       <c r="D17" t="n">
-        <v>1.317</v>
+        <v>1.26</v>
       </c>
       <c r="E17" t="n">
-        <v>4.3032</v>
+        <v>4.2769</v>
       </c>
       <c r="F17" t="n">
-        <v>4.9885</v>
+        <v>4.9622</v>
       </c>
       <c r="G17" t="n">
         <v>-0.6853</v>
       </c>
       <c r="H17" t="n">
-        <v>5.5188</v>
+        <v>5.4777</v>
       </c>
       <c r="I17" t="n">
         <v>5.5703</v>
@@ -1232,25 +1232,25 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4.0176</v>
+        <v>3.9952</v>
       </c>
       <c r="C18" t="n">
-        <v>0.8013</v>
+        <v>0.7969000000000001</v>
       </c>
       <c r="D18" t="n">
-        <v>1.2017</v>
+        <v>1.1478</v>
       </c>
       <c r="E18" t="n">
-        <v>4.0176</v>
+        <v>3.9952</v>
       </c>
       <c r="F18" t="n">
-        <v>3.0151</v>
+        <v>2.9927</v>
       </c>
       <c r="G18" t="n">
         <v>1.0025</v>
       </c>
       <c r="H18" t="n">
-        <v>3.0151</v>
+        <v>2.9927</v>
       </c>
       <c r="I18" t="n">
         <v>3.0433</v>
@@ -1284,7 +1284,7 @@
         <v>0.7905</v>
       </c>
       <c r="D19" t="n">
-        <v>1.1798</v>
+        <v>1.1351</v>
       </c>
       <c r="E19" t="n">
         <v>3.9634</v>
@@ -1330,7 +1330,7 @@
         <v>0.7712</v>
       </c>
       <c r="D20" t="n">
-        <v>1.1405</v>
+        <v>1.0964</v>
       </c>
       <c r="E20" t="n">
         <v>3.8663</v>
@@ -1370,25 +1370,25 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3.7493</v>
+        <v>3.7353</v>
       </c>
       <c r="C21" t="n">
-        <v>0.7478</v>
+        <v>0.745</v>
       </c>
       <c r="D21" t="n">
-        <v>1.0933</v>
+        <v>1.0442</v>
       </c>
       <c r="E21" t="n">
-        <v>3.7493</v>
+        <v>3.7353</v>
       </c>
       <c r="F21" t="n">
-        <v>3.7493</v>
+        <v>3.7353</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>3.7493</v>
+        <v>3.7353</v>
       </c>
       <c r="I21" t="n">
         <v>3.7667</v>
@@ -1416,25 +1416,25 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3.6375</v>
+        <v>3.624</v>
       </c>
       <c r="C22" t="n">
-        <v>0.7255</v>
+        <v>0.7228</v>
       </c>
       <c r="D22" t="n">
-        <v>1.0481</v>
+        <v>0.9999</v>
       </c>
       <c r="E22" t="n">
-        <v>3.6375</v>
+        <v>3.624</v>
       </c>
       <c r="F22" t="n">
-        <v>3.6375</v>
+        <v>3.624</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>3.6375</v>
+        <v>3.624</v>
       </c>
       <c r="I22" t="n">
         <v>3.6545</v>
@@ -1468,7 +1468,7 @@
         <v>0.6931</v>
       </c>
       <c r="D23" t="n">
-        <v>0.9825</v>
+        <v>0.9405</v>
       </c>
       <c r="E23" t="n">
         <v>3.475</v>
@@ -1514,7 +1514,7 @@
         <v>0.6294</v>
       </c>
       <c r="D24" t="n">
-        <v>0.8535</v>
+        <v>0.8133</v>
       </c>
       <c r="E24" t="n">
         <v>3.1557</v>
@@ -1554,25 +1554,25 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3.1416</v>
+        <v>3.1196</v>
       </c>
       <c r="C25" t="n">
-        <v>0.6266</v>
+        <v>0.6222</v>
       </c>
       <c r="D25" t="n">
-        <v>0.8478</v>
+        <v>0.7989000000000001</v>
       </c>
       <c r="E25" t="n">
-        <v>3.1416</v>
+        <v>3.1196</v>
       </c>
       <c r="F25" t="n">
-        <v>2.9556</v>
+        <v>2.9336</v>
       </c>
       <c r="G25" t="n">
         <v>0.186</v>
       </c>
       <c r="H25" t="n">
-        <v>2.9556</v>
+        <v>2.9336</v>
       </c>
       <c r="I25" t="n">
         <v>2.9832</v>
@@ -1600,25 +1600,25 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.078</v>
+        <v>3.0665</v>
       </c>
       <c r="C26" t="n">
-        <v>0.6139</v>
+        <v>0.6116</v>
       </c>
       <c r="D26" t="n">
-        <v>0.8221000000000001</v>
+        <v>0.7778</v>
       </c>
       <c r="E26" t="n">
-        <v>3.078</v>
+        <v>3.0665</v>
       </c>
       <c r="F26" t="n">
-        <v>3.078</v>
+        <v>3.0665</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>3.078</v>
+        <v>3.0665</v>
       </c>
       <c r="I26" t="n">
         <v>3.0923</v>
@@ -1646,25 +1646,25 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2.9412</v>
+        <v>2.9189</v>
       </c>
       <c r="C27" t="n">
-        <v>0.5866</v>
+        <v>0.5822000000000001</v>
       </c>
       <c r="D27" t="n">
-        <v>0.7668</v>
+        <v>0.719</v>
       </c>
       <c r="E27" t="n">
-        <v>2.9412</v>
+        <v>2.9189</v>
       </c>
       <c r="F27" t="n">
-        <v>2.9928</v>
+        <v>2.9705</v>
       </c>
       <c r="G27" t="n">
         <v>-0.0516</v>
       </c>
       <c r="H27" t="n">
-        <v>2.9928</v>
+        <v>2.9705</v>
       </c>
       <c r="I27" t="n">
         <v>3.0207</v>
@@ -1698,7 +1698,7 @@
         <v>0.4494</v>
       </c>
       <c r="D28" t="n">
-        <v>0.4889</v>
+        <v>0.4538</v>
       </c>
       <c r="E28" t="n">
         <v>2.2532</v>
@@ -1744,7 +1744,7 @@
         <v>0.4423</v>
       </c>
       <c r="D29" t="n">
-        <v>0.4745</v>
+        <v>0.4396</v>
       </c>
       <c r="E29" t="n">
         <v>2.2177</v>
@@ -1780,93 +1780,93 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Twistzz</t>
+          <t>pesadelo</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2.1833</v>
+        <v>2.1322</v>
       </c>
       <c r="C30" t="n">
-        <v>0.4355</v>
+        <v>0.4253</v>
       </c>
       <c r="D30" t="n">
-        <v>0.4606</v>
+        <v>0.4056</v>
       </c>
       <c r="E30" t="n">
-        <v>2.1833</v>
+        <v>2.1322</v>
       </c>
       <c r="F30" t="n">
-        <v>3.0193</v>
+        <v>0.9127</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.836</v>
+        <v>1.2195</v>
       </c>
       <c r="H30" t="n">
-        <v>3.0193</v>
+        <v>0.9127</v>
       </c>
       <c r="I30" t="n">
-        <v>3.0902</v>
+        <v>0.9127</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.836</v>
+        <v>1.2195</v>
       </c>
       <c r="K30" t="n">
-        <v>325</v>
+        <v>388</v>
       </c>
       <c r="L30" t="n">
-        <v>105</v>
+        <v>128</v>
       </c>
       <c r="M30" t="n">
-        <v>2.2542</v>
+        <v>2.1322</v>
       </c>
       <c r="N30" t="n">
-        <v>430</v>
+        <v>516</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>pesadelo</t>
+          <t>Twistzz</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>2.1322</v>
+        <v>2.1274</v>
       </c>
       <c r="C31" t="n">
-        <v>0.4253</v>
+        <v>0.4243</v>
       </c>
       <c r="D31" t="n">
-        <v>0.44</v>
+        <v>0.4036</v>
       </c>
       <c r="E31" t="n">
-        <v>2.1322</v>
+        <v>2.1274</v>
       </c>
       <c r="F31" t="n">
-        <v>0.9127</v>
+        <v>2.9634</v>
       </c>
       <c r="G31" t="n">
-        <v>1.2195</v>
+        <v>-0.836</v>
       </c>
       <c r="H31" t="n">
-        <v>0.9127</v>
+        <v>2.9634</v>
       </c>
       <c r="I31" t="n">
-        <v>0.9127</v>
+        <v>3.0902</v>
       </c>
       <c r="J31" t="n">
-        <v>1.2195</v>
+        <v>-0.836</v>
       </c>
       <c r="K31" t="n">
-        <v>388</v>
+        <v>325</v>
       </c>
       <c r="L31" t="n">
-        <v>128</v>
+        <v>105</v>
       </c>
       <c r="M31" t="n">
-        <v>2.1322</v>
+        <v>2.2542</v>
       </c>
       <c r="N31" t="n">
-        <v>516</v>
+        <v>430</v>
       </c>
     </row>
     <row r="32">
@@ -1882,7 +1882,7 @@
         <v>0.3659</v>
       </c>
       <c r="D32" t="n">
-        <v>0.3197</v>
+        <v>0.287</v>
       </c>
       <c r="E32" t="n">
         <v>1.8345</v>
@@ -1928,7 +1928,7 @@
         <v>0.3534</v>
       </c>
       <c r="D33" t="n">
-        <v>0.2945</v>
+        <v>0.2621</v>
       </c>
       <c r="E33" t="n">
         <v>1.772</v>
@@ -1974,7 +1974,7 @@
         <v>0.3461</v>
       </c>
       <c r="D34" t="n">
-        <v>0.2795</v>
+        <v>0.2473</v>
       </c>
       <c r="E34" t="n">
         <v>1.735</v>
@@ -2020,7 +2020,7 @@
         <v>0.3192</v>
       </c>
       <c r="D35" t="n">
-        <v>0.2252</v>
+        <v>0.1937</v>
       </c>
       <c r="E35" t="n">
         <v>1.6005</v>
@@ -2066,7 +2066,7 @@
         <v>0.1789</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.0591</v>
+        <v>-0.0867</v>
       </c>
       <c r="E36" t="n">
         <v>0.8967000000000001</v>
@@ -2112,7 +2112,7 @@
         <v>0.1714</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.0743</v>
+        <v>-0.1016</v>
       </c>
       <c r="E37" t="n">
         <v>0.8591</v>
@@ -2158,7 +2158,7 @@
         <v>0.1657</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.0858</v>
+        <v>-0.113</v>
       </c>
       <c r="E38" t="n">
         <v>0.8306</v>
@@ -2198,25 +2198,25 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.6395999999999999</v>
+        <v>0.6372</v>
       </c>
       <c r="C39" t="n">
-        <v>0.1276</v>
+        <v>0.1271</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.163</v>
+        <v>-0.19</v>
       </c>
       <c r="E39" t="n">
-        <v>0.6395999999999999</v>
+        <v>0.6372</v>
       </c>
       <c r="F39" t="n">
-        <v>0.6395999999999999</v>
+        <v>0.6372</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>0.6395999999999999</v>
+        <v>0.6372</v>
       </c>
       <c r="I39" t="n">
         <v>0.6425999999999999</v>
@@ -2250,7 +2250,7 @@
         <v>0.09760000000000001</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.2237</v>
+        <v>-0.249</v>
       </c>
       <c r="E40" t="n">
         <v>0.4893</v>
@@ -2296,7 +2296,7 @@
         <v>0.0535</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.3131</v>
+        <v>-0.3371</v>
       </c>
       <c r="E41" t="n">
         <v>0.2681</v>
@@ -2336,25 +2336,25 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.2523</v>
+        <v>0.2292</v>
       </c>
       <c r="C42" t="n">
-        <v>0.0503</v>
+        <v>0.0457</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.3194</v>
+        <v>-0.3526</v>
       </c>
       <c r="E42" t="n">
-        <v>0.2523</v>
+        <v>0.2292</v>
       </c>
       <c r="F42" t="n">
-        <v>1.2523</v>
+        <v>1.2292</v>
       </c>
       <c r="G42" t="n">
         <v>-1</v>
       </c>
       <c r="H42" t="n">
-        <v>1.2523</v>
+        <v>1.2292</v>
       </c>
       <c r="I42" t="n">
         <v>1.2818</v>
@@ -2388,7 +2388,7 @@
         <v>0.0356</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.3493</v>
+        <v>-0.3728</v>
       </c>
       <c r="E43" t="n">
         <v>0.1785</v>
@@ -2434,7 +2434,7 @@
         <v>-0.1129</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.6501</v>
+        <v>-0.6695</v>
       </c>
       <c r="E44" t="n">
         <v>-0.5662</v>
@@ -2480,7 +2480,7 @@
         <v>-0.1402</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.7053</v>
+        <v>-0.7239</v>
       </c>
       <c r="E45" t="n">
         <v>-0.7029</v>
@@ -2526,7 +2526,7 @@
         <v>-0.1726</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.771</v>
+        <v>-0.7887</v>
       </c>
       <c r="E46" t="n">
         <v>-0.8653999999999999</v>
@@ -2572,7 +2572,7 @@
         <v>-0.1752</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.7762</v>
+        <v>-0.7939000000000001</v>
       </c>
       <c r="E47" t="n">
         <v>-0.8784</v>
@@ -2618,7 +2618,7 @@
         <v>-0.2353</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.898</v>
+        <v>-0.9139</v>
       </c>
       <c r="E48" t="n">
         <v>-1.1798</v>
@@ -2664,7 +2664,7 @@
         <v>-0.2707</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.9697</v>
+        <v>-0.9847</v>
       </c>
       <c r="E49" t="n">
         <v>-1.3573</v>
@@ -2704,25 +2704,25 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>-1.399</v>
+        <v>-1.3954</v>
       </c>
       <c r="C50" t="n">
-        <v>-0.279</v>
+        <v>-0.2783</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.9865</v>
+        <v>-0.9998</v>
       </c>
       <c r="E50" t="n">
-        <v>-1.399</v>
+        <v>-1.3954</v>
       </c>
       <c r="F50" t="n">
-        <v>-0.4891</v>
+        <v>-0.4855</v>
       </c>
       <c r="G50" t="n">
         <v>-0.9099</v>
       </c>
       <c r="H50" t="n">
-        <v>-0.4891</v>
+        <v>-0.4855</v>
       </c>
       <c r="I50" t="n">
         <v>-0.4937</v>
@@ -2756,7 +2756,7 @@
         <v>-0.2912</v>
       </c>
       <c r="D51" t="n">
-        <v>-1.0112</v>
+        <v>-1.0256</v>
       </c>
       <c r="E51" t="n">
         <v>-1.46</v>
@@ -2802,7 +2802,7 @@
         <v>-0.3329</v>
       </c>
       <c r="D52" t="n">
-        <v>-1.0956</v>
+        <v>-1.1088</v>
       </c>
       <c r="E52" t="n">
         <v>-1.6689</v>
@@ -2848,7 +2848,7 @@
         <v>-0.4045</v>
       </c>
       <c r="D53" t="n">
-        <v>-1.2405</v>
+        <v>-1.2518</v>
       </c>
       <c r="E53" t="n">
         <v>-2.0278</v>
@@ -2894,7 +2894,7 @@
         <v>-0.4773</v>
       </c>
       <c r="D54" t="n">
-        <v>-1.388</v>
+        <v>-1.3972</v>
       </c>
       <c r="E54" t="n">
         <v>-2.3928</v>
@@ -2940,7 +2940,7 @@
         <v>-0.5426</v>
       </c>
       <c r="D55" t="n">
-        <v>-1.5203</v>
+        <v>-1.5276</v>
       </c>
       <c r="E55" t="n">
         <v>-2.7202</v>
@@ -2986,7 +2986,7 @@
         <v>-0.5461</v>
       </c>
       <c r="D56" t="n">
-        <v>-1.5274</v>
+        <v>-1.5347</v>
       </c>
       <c r="E56" t="n">
         <v>-2.7379</v>
@@ -3032,7 +3032,7 @@
         <v>-0.6584</v>
       </c>
       <c r="D57" t="n">
-        <v>-1.7549</v>
+        <v>-1.7591</v>
       </c>
       <c r="E57" t="n">
         <v>-3.3011</v>
@@ -3078,7 +3078,7 @@
         <v>-0.6696</v>
       </c>
       <c r="D58" t="n">
-        <v>-1.7776</v>
+        <v>-1.7815</v>
       </c>
       <c r="E58" t="n">
         <v>-3.3573</v>
@@ -3124,7 +3124,7 @@
         <v>-0.6827</v>
       </c>
       <c r="D59" t="n">
-        <v>-1.8042</v>
+        <v>-1.8076</v>
       </c>
       <c r="E59" t="n">
         <v>-3.423</v>
@@ -3164,25 +3164,25 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-3.6692</v>
+        <v>-3.6448</v>
       </c>
       <c r="C60" t="n">
-        <v>-0.7319</v>
+        <v>-0.727</v>
       </c>
       <c r="D60" t="n">
-        <v>-1.9036</v>
+        <v>-1.896</v>
       </c>
       <c r="E60" t="n">
-        <v>-3.6692</v>
+        <v>-3.6448</v>
       </c>
       <c r="F60" t="n">
-        <v>-3.2709</v>
+        <v>-3.2465</v>
       </c>
       <c r="G60" t="n">
         <v>-0.3983</v>
       </c>
       <c r="H60" t="n">
-        <v>-3.2709</v>
+        <v>-3.2465</v>
       </c>
       <c r="I60" t="n">
         <v>-3.3014</v>
@@ -3216,7 +3216,7 @@
         <v>-0.8136</v>
       </c>
       <c r="D61" t="n">
-        <v>-2.0692</v>
+        <v>-2.069</v>
       </c>
       <c r="E61" t="n">
         <v>-4.079</v>
@@ -3262,7 +3262,7 @@
         <v>-0.8309</v>
       </c>
       <c r="D62" t="n">
-        <v>-2.1042</v>
+        <v>-2.1035</v>
       </c>
       <c r="E62" t="n">
         <v>-4.1656</v>
